--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00930-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00930-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E03CAABA-E2C2-4089-A315-722077204F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0ED27EAA-5EE2-4E84-A5DB-86AE2D7F99BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{A77C0AAE-E513-48E5-B9F1-7B854975D7DE}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{451E691E-F5F8-4C2D-8B44-196A8CB869EA}"/>
   </bookViews>
   <sheets>
     <sheet name="00930-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1651,25 +1651,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBCB3269-FFE9-44A6-B1D3-2B3B0C3F633F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3911F7CD-2CA4-403C-909C-9584C57FB4C9}">
   <dimension ref="A1:R48"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" customWidth="1"/>
-    <col min="4" max="4" width="8.21875" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" customWidth="1"/>
-    <col min="6" max="6" width="8.21875" customWidth="1"/>
-    <col min="7" max="9" width="7.88671875" customWidth="1"/>
-    <col min="10" max="10" width="8.21875" customWidth="1"/>
-    <col min="11" max="13" width="7.88671875" customWidth="1"/>
-    <col min="14" max="14" width="8.21875" customWidth="1"/>
-    <col min="15" max="17" width="7.88671875" customWidth="1"/>
-    <col min="18" max="18" width="9.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="12.875" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1697,7 +1697,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1727,7 +1727,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1823,7 +1823,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2026</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="44"/>
       <c r="C6" s="46"/>
@@ -1903,7 +1903,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="45" t="s">
         <v>27</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="51"/>
       <c r="B8" s="51"/>
       <c r="C8" s="16" t="s">
@@ -1981,7 +1981,7 @@
       <c r="Q8" s="52"/>
       <c r="R8" s="52"/>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="46"/>
       <c r="B9" s="46"/>
       <c r="C9" s="17" t="s">
@@ -2003,7 +2003,7 @@
       <c r="Q9" s="48"/>
       <c r="R9" s="48"/>
     </row>
-    <row r="10" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="57">
         <v>2025</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="59" t="s">
         <v>27</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="60"/>
       <c r="B12" s="60"/>
       <c r="C12" s="23" t="s">
@@ -2135,7 +2135,7 @@
       <c r="Q12" s="63"/>
       <c r="R12" s="63"/>
     </row>
-    <row r="13" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="24" t="s">
@@ -2157,7 +2157,7 @@
       <c r="Q13" s="64"/>
       <c r="R13" s="64"/>
     </row>
-    <row r="14" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="59" t="s">
         <v>27</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="60"/>
       <c r="B15" s="60"/>
       <c r="C15" s="23" t="s">
@@ -2235,7 +2235,7 @@
       <c r="Q15" s="63"/>
       <c r="R15" s="63"/>
     </row>
-    <row r="16" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="61"/>
       <c r="B16" s="61"/>
       <c r="C16" s="24" t="s">
@@ -2257,7 +2257,7 @@
       <c r="Q16" s="64"/>
       <c r="R16" s="64"/>
     </row>
-    <row r="17" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="59" t="s">
         <v>27</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="60"/>
       <c r="B18" s="60"/>
       <c r="C18" s="23" t="s">
@@ -2335,7 +2335,7 @@
       <c r="Q18" s="63"/>
       <c r="R18" s="63"/>
     </row>
-    <row r="19" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="24" t="s">
@@ -2357,7 +2357,7 @@
       <c r="Q19" s="64"/>
       <c r="R19" s="64"/>
     </row>
-    <row r="20" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="59" t="s">
         <v>27</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="60"/>
       <c r="B21" s="60"/>
       <c r="C21" s="23" t="s">
@@ -2435,7 +2435,7 @@
       <c r="Q21" s="63"/>
       <c r="R21" s="63"/>
     </row>
-    <row r="22" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="61"/>
       <c r="B22" s="61"/>
       <c r="C22" s="24" t="s">
@@ -2457,7 +2457,7 @@
       <c r="Q22" s="64"/>
       <c r="R22" s="64"/>
     </row>
-    <row r="23" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="59" t="s">
         <v>27</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="60"/>
       <c r="B24" s="60"/>
       <c r="C24" s="23" t="s">
@@ -2535,7 +2535,7 @@
       <c r="Q24" s="63"/>
       <c r="R24" s="63"/>
     </row>
-    <row r="25" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="61"/>
       <c r="B25" s="61"/>
       <c r="C25" s="24" t="s">
@@ -2557,7 +2557,7 @@
       <c r="Q25" s="64"/>
       <c r="R25" s="64"/>
     </row>
-    <row r="26" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="59" t="s">
         <v>27</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="60"/>
       <c r="B27" s="60"/>
       <c r="C27" s="23" t="s">
@@ -2635,7 +2635,7 @@
       <c r="Q27" s="63"/>
       <c r="R27" s="63"/>
     </row>
-    <row r="28" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="61"/>
       <c r="B28" s="61"/>
       <c r="C28" s="24" t="s">
@@ -2657,7 +2657,7 @@
       <c r="Q28" s="64"/>
       <c r="R28" s="64"/>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="71">
         <v>2024</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="45" t="s">
         <v>27</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="51"/>
       <c r="B31" s="51"/>
       <c r="C31" s="16" t="s">
@@ -2789,7 +2789,7 @@
       <c r="Q31" s="52"/>
       <c r="R31" s="52"/>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="46"/>
       <c r="B32" s="46"/>
       <c r="C32" s="17" t="s">
@@ -2811,7 +2811,7 @@
       <c r="Q32" s="48"/>
       <c r="R32" s="48"/>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="45" t="s">
         <v>27</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="51"/>
       <c r="B34" s="51"/>
       <c r="C34" s="16" t="s">
@@ -2889,7 +2889,7 @@
       <c r="Q34" s="52"/>
       <c r="R34" s="52"/>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="46"/>
       <c r="B35" s="46"/>
       <c r="C35" s="17" t="s">
@@ -2911,7 +2911,7 @@
       <c r="Q35" s="48"/>
       <c r="R35" s="48"/>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="45" t="s">
         <v>27</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="51"/>
       <c r="B37" s="51"/>
       <c r="C37" s="16" t="s">
@@ -2989,7 +2989,7 @@
       <c r="Q37" s="52"/>
       <c r="R37" s="52"/>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="46"/>
       <c r="B38" s="46"/>
       <c r="C38" s="17" t="s">
@@ -3011,7 +3011,7 @@
       <c r="Q38" s="48"/>
       <c r="R38" s="48"/>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="45" t="s">
         <v>27</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="51"/>
       <c r="B40" s="51"/>
       <c r="C40" s="16" t="s">
@@ -3089,7 +3089,7 @@
       <c r="Q40" s="52"/>
       <c r="R40" s="52"/>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="46"/>
       <c r="B41" s="46"/>
       <c r="C41" s="17" t="s">
@@ -3111,7 +3111,7 @@
       <c r="Q41" s="48"/>
       <c r="R41" s="48"/>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="45" t="s">
         <v>27</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="51"/>
       <c r="B43" s="51"/>
       <c r="C43" s="16" t="s">
@@ -3189,7 +3189,7 @@
       <c r="Q43" s="52"/>
       <c r="R43" s="52"/>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="46"/>
       <c r="B44" s="46"/>
       <c r="C44" s="17" t="s">
@@ -3211,7 +3211,7 @@
       <c r="Q44" s="48"/>
       <c r="R44" s="48"/>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="45" t="s">
         <v>27</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="51"/>
       <c r="B46" s="51"/>
       <c r="C46" s="16" t="s">
@@ -3289,7 +3289,7 @@
       <c r="Q46" s="52"/>
       <c r="R46" s="52"/>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="46"/>
       <c r="B47" s="46"/>
       <c r="C47" s="17" t="s">
@@ -3311,7 +3311,7 @@
       <c r="Q47" s="48"/>
       <c r="R47" s="48"/>
     </row>
-    <row r="48" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="57" t="s">
         <v>68</v>
       </c>
